--- a/Result/profitability/3323.xlsx
+++ b/Result/profitability/3323.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.27625</v>
+        <v>-0.30625</v>
       </c>
       <c r="N2" t="n">
-        <v>9.4</v>
+        <v>9.268750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.21875</v>
+        <v>-0.2225</v>
       </c>
       <c r="N3" t="n">
-        <v>9.732499999999998</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="N4" t="n">
-        <v>10.3175</v>
+        <v>10.08875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>0.33625</v>
+        <v>0.39125</v>
       </c>
       <c r="N5" t="n">
-        <v>10.39375</v>
+        <v>10.88125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.57375</v>
+        <v>0.55375</v>
       </c>
       <c r="N6" t="n">
-        <v>11.1575</v>
+        <v>11.1225</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6475</v>
+        <v>0.63875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.5775</v>
+        <v>11.2575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.8674999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>11.61125</v>
+        <v>11.6275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-57</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-4.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-41</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.84375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2500000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.129999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01533018867924518</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5116279069767442</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8280254777070062</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
